--- a/upload/продажи08.06+ рц.xlsx
+++ b/upload/продажи08.06+ рц.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.10.10.120\Shares-Office\Розница\Смирнов А\Июнь 26\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E204204A-D3F9-4F30-871C-8877984DE78F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA33FE50-4C11-43A5-A75B-0C41A3A518D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3225" yWindow="-120" windowWidth="25695" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
